--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/03062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/03062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miércoles, 3 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Marcos
-Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
-*Oración de la mañana*
-Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
-Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
-Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
-En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>miércoles, 3 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 18-27 En aquel tiempo, fueron a ver a Jesús algunos de los saduceos, los cuales afirman que los muertos no resucitan, y le dijeron: “Maestro, Moisés nos dejó escrito que si un hombre muere dejando a su viuda sin hijos, que la tome por mujer el hermano del que murió, para darle descendencia a su hermano. Había una vez siete hermanos, el primero de los cuales se casó y murió sin dejar hijos. El segundo se casó con la viuda y murió también, sin dejar hijos; lo mismo el tercero. Los siete se casaron con ella y ninguno de ellos dejó descendencia. Por último, después de todos, murió también la mujer. El día de la resurrección, cuando resuciten de entre los muertos, ¿de cuál de los siete será mujer? Porque fue mujer de los siete”. Jesús les contestó: “Están en un error, porque no entienden las Escrituras ni el poder de Dios. Pues cuando resuciten de entre los muertos, ni los hombres tendrán mujer ni las mujeres marido, sino que serán como los ángeles del cielo. Y en cuanto al hecho de que los muertos resucitan, ¿acaso no han leído en el libro de Moisés aquel pasaje de la zarza, en que Dios le dijo: Yo soy el Dios de Abraham, el Dios de Isaac, el Dios de Jacob? Dios no es Dios de muertos, sino de vivos. Están, pues, muy equivocados”.
+*Oración de la mañana*
+Querido Jesús, Tú que nos enseñas a comprender las verdades eternas, ilumina nuestra mente para que podamos entender las Escrituras y tu mensaje de vida. Ayúdanos a trascender nuestras limitaciones humanas y terrenales para abrazar la vida eterna que ofreces. Enséñanos a vivir en la plenitud de tu amor, sabiendo que no somos seres destinados a la muerte, sino a la vida.
+Gracias, Padre Celestial, por este nuevo día que nos ofreces. Gracias por tu amor incondicional y por tu poder divino que nos levanta de la muerte a la vida. Ayúdanos a recordar siempre que eres un Dios de vivos y que en ti, encontramos la promesa de la resurrección y la vida eterna.
+Espíritu Santo, soplo de vida, guíanos hoy para vivir de acuerdo a las verdades del Evangelio. Infunde en nosotros sabiduría y entendimiento para que podamos mirar más allá de nuestras preocupaciones terrenales y centrarnos en la vida eterna que Dios nos ofrece. Ayúdanos a ser como los ángeles del cielo, viviendo en amor y unidad, siempre fieles a la voluntad de Dios.
+En la trinidad sagrada de Jesús, Padre y Espíritu Santo, confiamos y nos entregamos. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>